--- a/Unity/Assets/Config/Excel/PetSkinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetSkinConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B976E-16EE-42C1-89EF-C3A517FC70D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E3E663-5878-441B-BA62-1A85F4D94CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,9 +211,6 @@
     <t>绿林熊妖</t>
   </si>
   <si>
-    <t>山贼</t>
-  </si>
-  <si>
     <t>森林蜘蛛</t>
   </si>
   <si>
@@ -265,9 +262,6 @@
     <t>冰灵蜘蛛</t>
   </si>
   <si>
-    <t>雪狼</t>
-  </si>
-  <si>
     <t>冰灵山羊</t>
   </si>
   <si>
@@ -323,6 +317,14 @@
   </si>
   <si>
     <t>天狼蜘蛛</t>
+  </si>
+  <si>
+    <t>绿石怪</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰狼</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2385,7 +2387,7 @@
         <v>310105</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="E13" s="7">
         <v>310105</v>
@@ -2404,7 +2406,7 @@
         <v>310106</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="7">
         <v>310106</v>
@@ -2423,7 +2425,7 @@
         <v>310107</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="7">
         <v>310107</v>
@@ -2442,7 +2444,7 @@
         <v>320101</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7">
         <v>320101</v>
@@ -2461,7 +2463,7 @@
         <v>320102</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="7">
         <v>320102</v>
@@ -2480,7 +2482,7 @@
         <v>320103</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" s="7">
         <v>320103</v>
@@ -2499,7 +2501,7 @@
         <v>320104</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" s="7">
         <v>320104</v>
@@ -2518,7 +2520,7 @@
         <v>320105</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="7">
         <v>320105</v>
@@ -2537,7 +2539,7 @@
         <v>320106</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" s="7">
         <v>320106</v>
@@ -2556,7 +2558,7 @@
         <v>320107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" s="7">
         <v>320107</v>
@@ -2575,7 +2577,7 @@
         <v>330101</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="7">
         <v>330101</v>
@@ -2594,7 +2596,7 @@
         <v>330102</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="7">
         <v>330102</v>
@@ -2613,7 +2615,7 @@
         <v>330103</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" s="7">
         <v>330103</v>
@@ -2632,7 +2634,7 @@
         <v>330104</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" s="7">
         <v>330104</v>
@@ -2651,7 +2653,7 @@
         <v>330105</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="7">
         <v>330105</v>
@@ -2670,7 +2672,7 @@
         <v>330106</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" s="7">
         <v>330106</v>
@@ -2689,7 +2691,7 @@
         <v>330107</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" s="7">
         <v>330107</v>
@@ -2708,7 +2710,7 @@
         <v>340101</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="7">
         <v>340101</v>
@@ -2727,7 +2729,7 @@
         <v>340102</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E31" s="7">
         <v>340102</v>
@@ -2746,7 +2748,7 @@
         <v>340103</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E32" s="7">
         <v>340103</v>
@@ -2765,7 +2767,7 @@
         <v>340104</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E33" s="7">
         <v>340104</v>
@@ -2784,7 +2786,7 @@
         <v>340105</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E34" s="7">
         <v>340105</v>
@@ -2803,7 +2805,7 @@
         <v>340106</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" s="7">
         <v>340106</v>
@@ -2822,7 +2824,7 @@
         <v>340107</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E36" s="7">
         <v>340107</v>
@@ -2841,7 +2843,7 @@
         <v>350101</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" s="7">
         <v>350101</v>
@@ -2860,7 +2862,7 @@
         <v>350102</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E38" s="7">
         <v>350102</v>
@@ -2879,7 +2881,7 @@
         <v>350103</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E39" s="7">
         <v>350103</v>
@@ -2898,7 +2900,7 @@
         <v>350104</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E40" s="7">
         <v>350104</v>
@@ -2917,7 +2919,7 @@
         <v>350105</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E41" s="7">
         <v>350105</v>
@@ -2936,7 +2938,7 @@
         <v>350106</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E42" s="7">
         <v>350106</v>
@@ -2955,7 +2957,7 @@
         <v>400001</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E43" s="7">
         <v>400001</v>
@@ -2974,7 +2976,7 @@
         <v>400002</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" s="7">
         <v>400002</v>
@@ -2993,7 +2995,7 @@
         <v>400003</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" s="7">
         <v>400003</v>
@@ -3012,7 +3014,7 @@
         <v>400004</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E46" s="7">
         <v>400004</v>
@@ -3031,7 +3033,7 @@
         <v>400005</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E47" s="7">
         <v>400005</v>
@@ -3050,7 +3052,7 @@
         <v>400006</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E48" s="7">
         <v>400006</v>
@@ -3069,7 +3071,7 @@
         <v>400007</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="7">
         <v>400007</v>
@@ -3088,7 +3090,7 @@
         <v>400008</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E50" s="7">
         <v>400008</v>

--- a/Unity/Assets/Config/Excel/PetSkinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetSkinConfig.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E3E663-5878-441B-BA62-1A85F4D94CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="MysteryConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -70,6 +77,132 @@
     <t>神愈使者</t>
   </si>
   <si>
+    <t>软泥怪</t>
+  </si>
+  <si>
+    <t>森灵小妖</t>
+  </si>
+  <si>
+    <t>森灵小猪</t>
+  </si>
+  <si>
+    <t>绿林熊妖</t>
+  </si>
+  <si>
+    <t>绿石怪</t>
+  </si>
+  <si>
+    <t>森林蜘蛛</t>
+  </si>
+  <si>
+    <t>森林熊</t>
+  </si>
+  <si>
+    <t>绿洲龟</t>
+  </si>
+  <si>
+    <t>绿洲恐龙</t>
+  </si>
+  <si>
+    <t>绿洲蜗牛</t>
+  </si>
+  <si>
+    <t>荒漠鹰</t>
+  </si>
+  <si>
+    <t>迅捷恐龙</t>
+  </si>
+  <si>
+    <t>遗迹火焰</t>
+  </si>
+  <si>
+    <t>遗迹弓手</t>
+  </si>
+  <si>
+    <t>螃蟹护卫</t>
+  </si>
+  <si>
+    <t>猛虎</t>
+  </si>
+  <si>
+    <t>丛林虎</t>
+  </si>
+  <si>
+    <t>兽人护卫</t>
+  </si>
+  <si>
+    <t>地精守卫</t>
+  </si>
+  <si>
+    <t>兽人骑兵</t>
+  </si>
+  <si>
+    <t>岩石护卫</t>
+  </si>
+  <si>
+    <t>冰灵蜘蛛</t>
+  </si>
+  <si>
+    <t>冰狼</t>
+  </si>
+  <si>
+    <t>冰灵山羊</t>
+  </si>
+  <si>
+    <t>冰封蜗牛</t>
+  </si>
+  <si>
+    <t>冰块士兵</t>
+  </si>
+  <si>
+    <t>冰灵</t>
+  </si>
+  <si>
+    <t>冰块护卫</t>
+  </si>
+  <si>
+    <t>精灵蝴蝶</t>
+  </si>
+  <si>
+    <t>影月护卫</t>
+  </si>
+  <si>
+    <t>影月弓手</t>
+  </si>
+  <si>
+    <t>影月骑兵</t>
+  </si>
+  <si>
+    <t>暗灵士兵</t>
+  </si>
+  <si>
+    <t>熔岩护卫</t>
+  </si>
+  <si>
+    <t>邪恶鳄鱼</t>
+  </si>
+  <si>
+    <t>火焰松鼠</t>
+  </si>
+  <si>
+    <t>白羽蝴蝶</t>
+  </si>
+  <si>
+    <t>冰雪人</t>
+  </si>
+  <si>
+    <t>火焰之树</t>
+  </si>
+  <si>
+    <t>天空守卫</t>
+  </si>
+  <si>
+    <t>熔岩之魔</t>
+  </si>
+  <si>
+    <t>天狼蜘蛛</t>
+  </si>
+  <si>
     <t>呆呆</t>
   </si>
   <si>
@@ -197,141 +330,19 @@
   </si>
   <si>
     <t>神兽:仙界魔龙</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <t>森灵小妖</t>
-  </si>
-  <si>
-    <t>森灵小猪</t>
-  </si>
-  <si>
-    <t>绿林熊妖</t>
-  </si>
-  <si>
-    <t>森林蜘蛛</t>
-  </si>
-  <si>
-    <t>森林熊</t>
-  </si>
-  <si>
-    <t>绿洲龟</t>
-  </si>
-  <si>
-    <t>绿洲恐龙</t>
-  </si>
-  <si>
-    <t>绿洲蜗牛</t>
-  </si>
-  <si>
-    <t>荒漠鹰</t>
-  </si>
-  <si>
-    <t>迅捷恐龙</t>
-  </si>
-  <si>
-    <t>遗迹火焰</t>
-  </si>
-  <si>
-    <t>遗迹弓手</t>
-  </si>
-  <si>
-    <t>螃蟹护卫</t>
-  </si>
-  <si>
-    <t>猛虎</t>
-  </si>
-  <si>
-    <t>丛林虎</t>
-  </si>
-  <si>
-    <t>兽人护卫</t>
-  </si>
-  <si>
-    <t>地精守卫</t>
-  </si>
-  <si>
-    <t>兽人骑兵</t>
-  </si>
-  <si>
-    <t>岩石护卫</t>
-  </si>
-  <si>
-    <t>冰灵蜘蛛</t>
-  </si>
-  <si>
-    <t>冰灵山羊</t>
-  </si>
-  <si>
-    <t>冰封蜗牛</t>
-  </si>
-  <si>
-    <t>冰块士兵</t>
-  </si>
-  <si>
-    <t>冰灵</t>
-  </si>
-  <si>
-    <t>冰块护卫</t>
-  </si>
-  <si>
-    <t>精灵蝴蝶</t>
-  </si>
-  <si>
-    <t>影月护卫</t>
-  </si>
-  <si>
-    <t>影月弓手</t>
-  </si>
-  <si>
-    <t>影月骑兵</t>
-  </si>
-  <si>
-    <t>暗灵士兵</t>
-  </si>
-  <si>
-    <t>熔岩护卫</t>
-  </si>
-  <si>
-    <t>邪恶鳄鱼</t>
-  </si>
-  <si>
-    <t>火焰松鼠</t>
-  </si>
-  <si>
-    <t>冰雪人</t>
-  </si>
-  <si>
-    <t>火焰之树</t>
-  </si>
-  <si>
-    <t>天空守卫</t>
-  </si>
-  <si>
-    <t>白羽蝴蝶</t>
-  </si>
-  <si>
-    <t>熔岩之魔</t>
-  </si>
-  <si>
-    <t>天狼蜘蛛</t>
-  </si>
-  <si>
-    <t>绿石怪</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰狼</t>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,28 +353,25 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -371,21 +379,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -393,14 +398,12 @@
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -408,7 +411,157 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -416,15 +569,10 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,79 +593,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1498764000366222"/>
+        <fgColor theme="0" tint="-0.149876400036622"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79989013336588644"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79989013336588644"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79989013336588644"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79989013336588644"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79989013336588644"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -528,7 +862,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -577,936 +911,1163 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="314">
+  <cellStyleXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1517,344 +2078,392 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="293" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="293" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="293" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="293" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="293" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="314">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 4" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 6" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 7" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 5" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 6" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 7" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 5" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 6" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 7" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="61" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="62" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="64" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="66" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="68" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 4" xfId="71" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 5" xfId="73" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="74" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 6" xfId="75" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="78" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="80" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="81" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="82" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="83" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="84" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="85" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="86" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="88" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 4" xfId="90" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 5" xfId="92" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="93" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 6" xfId="94" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 7" xfId="95" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="100" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="102" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="103" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="104" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="105" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="108" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="110" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 5" xfId="111" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="112" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 6" xfId="113" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 7" xfId="114" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="115" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="116" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="117" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="118" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="119" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="120" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="121" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="122" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="123" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="124" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="125" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="126" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="127" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 4" xfId="128" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="129" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 5" xfId="130" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="131" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 6" xfId="132" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 7" xfId="133" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="134" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="136" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="137" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="138" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="139" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="140" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="141" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="143" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="144" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="145" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 6" xfId="151" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 7" xfId="152" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="153" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="154" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="155" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="157" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="158" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="159" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="160" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="161" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="162" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="163" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="164" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="165" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 4" xfId="166" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="167" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 5" xfId="168" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="169" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 6" xfId="170" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 7" xfId="171" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="173" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="174" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="176" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="177" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="178" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="181" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="182" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="184" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 4" xfId="185" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="186" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 5" xfId="187" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="188" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 6" xfId="189" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 7" xfId="190" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="191" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="192" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="194" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="195" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="196" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="197" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="198" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="199" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="200" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="201" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="202" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="203" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 4" xfId="204" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="205" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 5" xfId="206" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="207" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 6" xfId="208" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 7" xfId="209" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="210" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="211" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="213" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="214" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="215" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="216" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="217" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="218" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="219" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="220" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="222" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 4" xfId="223" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 5" xfId="225" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="226" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 6" xfId="227" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 7" xfId="228" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+  <cellStyles count="362">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="229" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="常规 2 2" xfId="230" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="常规 2 3" xfId="231" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="常规 2 3 2" xfId="232" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="233" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="常规 2 3 2 2 2 2" xfId="235" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="常规 2 3 2 2 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="常规 2 3 2 2 3" xfId="237" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="常规 2 3 2 2 3 2" xfId="238" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="常规 2 3 2 2 4" xfId="239" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="常规 2 3 2 2 4 2" xfId="240" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="常规 2 3 2 2 5" xfId="241" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="常规 2 3 2 2 6" xfId="242" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="243" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="常规 2 3 2 3 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="常规 2 3 2 3 3" xfId="245" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="常规 2 3 2 4" xfId="246" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="常规 2 3 2 4 2" xfId="247" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="常规 2 3 2 5" xfId="248" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="常规 2 3 2 5 2" xfId="249" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="常规 2 3 2 6" xfId="250" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="常规 2 3 2 7" xfId="251" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="常规 2 3 3" xfId="252" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="常规 2 3 3 2" xfId="253" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="常规 2 3 3 2 2" xfId="254" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="常规 2 3 3 2 3" xfId="255" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="常规 2 3 3 3" xfId="256" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="常规 2 3 3 3 2" xfId="257" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="常规 2 3 3 4" xfId="258" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="常规 2 3 3 4 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="常规 2 3 3 5" xfId="260" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="常规 2 3 3 6" xfId="261" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="常规 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="常规 2 3 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="常规 2 3 4 3" xfId="264" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="常规 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="常规 2 3 5 2" xfId="266" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="常规 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="常规 2 3 6 2" xfId="268" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="常规 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="常规 2 3 8" xfId="270" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="常规 3" xfId="271" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="常规 4" xfId="272" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="常规 5" xfId="273" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="常规 5 2" xfId="274" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="常规 5 2 2" xfId="275" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="常规 5 2 2 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="常规 5 2 2 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="常规 5 2 3" xfId="278" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="常规 5 2 3 2" xfId="279" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="常规 5 2 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="常规 5 2 4 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="常规 5 2 5" xfId="282" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="常规 5 2 6" xfId="283" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="常规 5 3" xfId="284" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="常规 5 3 2" xfId="285" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="常规 5 3 3" xfId="286" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="常规 5 4" xfId="287" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="常规 5 4 2" xfId="288" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="常规 5 5" xfId="289" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="常规 5 5 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="常规 5 6" xfId="291" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="常规 5 7" xfId="292" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="常规 6" xfId="293" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="注释 2" xfId="294" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="注释 2 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="注释 2 2 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="注释 2 2 2 2" xfId="297" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="注释 2 2 2 3" xfId="298" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="注释 2 2 3" xfId="299" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="注释 2 2 3 2" xfId="300" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="注释 2 2 4" xfId="301" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="注释 2 2 4 2" xfId="302" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="注释 2 2 5" xfId="303" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="注释 2 2 6" xfId="304" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="注释 2 3" xfId="305" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="注释 2 3 2" xfId="306" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="注释 2 3 3" xfId="307" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="注释 2 4" xfId="308" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="注释 2 4 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="注释 2 5" xfId="310" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="注释 2 5 2" xfId="311" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="注释 2 6" xfId="312" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="注释 2 7" xfId="313" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 1 4" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 1 5" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 1 6" xfId="66"/>
+    <cellStyle name="20% - 强调文字颜色 1 7" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="68"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="69"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="70"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="72"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="73"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="74"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="76"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="77"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="78"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="80"/>
+    <cellStyle name="20% - 强调文字颜色 2 4" xfId="81"/>
+    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="82"/>
+    <cellStyle name="20% - 强调文字颜色 2 5" xfId="83"/>
+    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="84"/>
+    <cellStyle name="20% - 强调文字颜色 2 6" xfId="85"/>
+    <cellStyle name="20% - 强调文字颜色 2 7" xfId="86"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="87"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="88"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="89"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="90"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="91"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="92"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="93"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="94"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="95"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="96"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="97"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="98"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="99"/>
+    <cellStyle name="20% - 强调文字颜色 3 4" xfId="100"/>
+    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="101"/>
+    <cellStyle name="20% - 强调文字颜色 3 5" xfId="102"/>
+    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="103"/>
+    <cellStyle name="20% - 强调文字颜色 3 6" xfId="104"/>
+    <cellStyle name="20% - 强调文字颜色 3 7" xfId="105"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="106"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="107"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="108"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="109"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="110"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="111"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="112"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="113"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="114"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="115"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="116"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="117"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="118"/>
+    <cellStyle name="20% - 强调文字颜色 4 4" xfId="119"/>
+    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="120"/>
+    <cellStyle name="20% - 强调文字颜色 4 5" xfId="121"/>
+    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="122"/>
+    <cellStyle name="20% - 强调文字颜色 4 6" xfId="123"/>
+    <cellStyle name="20% - 强调文字颜色 4 7" xfId="124"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="125"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="126"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="127"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="128"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="129"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="130"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="131"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="132"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="133"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="134"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="135"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="136"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="137"/>
+    <cellStyle name="20% - 强调文字颜色 5 4" xfId="138"/>
+    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="139"/>
+    <cellStyle name="20% - 强调文字颜色 5 5" xfId="140"/>
+    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="141"/>
+    <cellStyle name="20% - 强调文字颜色 5 6" xfId="142"/>
+    <cellStyle name="20% - 强调文字颜色 5 7" xfId="143"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="144"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="145"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="146"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="147"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="148"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="149"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="150"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="151"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="152"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="153"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="154"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="155"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="156"/>
+    <cellStyle name="20% - 强调文字颜色 6 4" xfId="157"/>
+    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="158"/>
+    <cellStyle name="20% - 强调文字颜色 6 5" xfId="159"/>
+    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="160"/>
+    <cellStyle name="20% - 强调文字颜色 6 6" xfId="161"/>
+    <cellStyle name="20% - 强调文字颜色 6 7" xfId="162"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="163"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="164"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="165"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="166"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="167"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="168"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="169"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="170"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="171"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="172"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="173"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="174"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="175"/>
+    <cellStyle name="40% - 强调文字颜色 1 4" xfId="176"/>
+    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="177"/>
+    <cellStyle name="40% - 强调文字颜色 1 5" xfId="178"/>
+    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="179"/>
+    <cellStyle name="40% - 强调文字颜色 1 6" xfId="180"/>
+    <cellStyle name="40% - 强调文字颜色 1 7" xfId="181"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="182"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="183"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="184"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="185"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="186"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="187"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="188"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="189"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="190"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="191"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="192"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="193"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="194"/>
+    <cellStyle name="40% - 强调文字颜色 2 4" xfId="195"/>
+    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="196"/>
+    <cellStyle name="40% - 强调文字颜色 2 5" xfId="197"/>
+    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="198"/>
+    <cellStyle name="40% - 强调文字颜色 2 6" xfId="199"/>
+    <cellStyle name="40% - 强调文字颜色 2 7" xfId="200"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="201"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="202"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="203"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="204"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="205"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="206"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="207"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="208"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="209"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="210"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="211"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="212"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="213"/>
+    <cellStyle name="40% - 强调文字颜色 3 4" xfId="214"/>
+    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="215"/>
+    <cellStyle name="40% - 强调文字颜色 3 5" xfId="216"/>
+    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="217"/>
+    <cellStyle name="40% - 强调文字颜色 3 6" xfId="218"/>
+    <cellStyle name="40% - 强调文字颜色 3 7" xfId="219"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="220"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="221"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="222"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="223"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="224"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="225"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="226"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="227"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="228"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="229"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="230"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="231"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="232"/>
+    <cellStyle name="40% - 强调文字颜色 4 4" xfId="233"/>
+    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="234"/>
+    <cellStyle name="40% - 强调文字颜色 4 5" xfId="235"/>
+    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="236"/>
+    <cellStyle name="40% - 强调文字颜色 4 6" xfId="237"/>
+    <cellStyle name="40% - 强调文字颜色 4 7" xfId="238"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="239"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="240"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="241"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="242"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="243"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="244"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="245"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="246"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="247"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="248"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="249"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="250"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="251"/>
+    <cellStyle name="40% - 强调文字颜色 5 4" xfId="252"/>
+    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="253"/>
+    <cellStyle name="40% - 强调文字颜色 5 5" xfId="254"/>
+    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="255"/>
+    <cellStyle name="40% - 强调文字颜色 5 6" xfId="256"/>
+    <cellStyle name="40% - 强调文字颜色 5 7" xfId="257"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="258"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="259"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="260"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="261"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="262"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="263"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="264"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="265"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="266"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="267"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="268"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="269"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="270"/>
+    <cellStyle name="40% - 强调文字颜色 6 4" xfId="271"/>
+    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="272"/>
+    <cellStyle name="40% - 强调文字颜色 6 5" xfId="273"/>
+    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="274"/>
+    <cellStyle name="40% - 强调文字颜色 6 6" xfId="275"/>
+    <cellStyle name="40% - 强调文字颜色 6 7" xfId="276"/>
+    <cellStyle name="常规 2" xfId="277"/>
+    <cellStyle name="常规 2 2" xfId="278"/>
+    <cellStyle name="常规 2 3" xfId="279"/>
+    <cellStyle name="常规 2 3 2" xfId="280"/>
+    <cellStyle name="常规 2 3 2 2" xfId="281"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="282"/>
+    <cellStyle name="常规 2 3 2 2 2 2" xfId="283"/>
+    <cellStyle name="常规 2 3 2 2 2 3" xfId="284"/>
+    <cellStyle name="常规 2 3 2 2 3" xfId="285"/>
+    <cellStyle name="常规 2 3 2 2 3 2" xfId="286"/>
+    <cellStyle name="常规 2 3 2 2 4" xfId="287"/>
+    <cellStyle name="常规 2 3 2 2 4 2" xfId="288"/>
+    <cellStyle name="常规 2 3 2 2 5" xfId="289"/>
+    <cellStyle name="常规 2 3 2 2 6" xfId="290"/>
+    <cellStyle name="常规 2 3 2 3" xfId="291"/>
+    <cellStyle name="常规 2 3 2 3 2" xfId="292"/>
+    <cellStyle name="常规 2 3 2 3 3" xfId="293"/>
+    <cellStyle name="常规 2 3 2 4" xfId="294"/>
+    <cellStyle name="常规 2 3 2 4 2" xfId="295"/>
+    <cellStyle name="常规 2 3 2 5" xfId="296"/>
+    <cellStyle name="常规 2 3 2 5 2" xfId="297"/>
+    <cellStyle name="常规 2 3 2 6" xfId="298"/>
+    <cellStyle name="常规 2 3 2 7" xfId="299"/>
+    <cellStyle name="常规 2 3 3" xfId="300"/>
+    <cellStyle name="常规 2 3 3 2" xfId="301"/>
+    <cellStyle name="常规 2 3 3 2 2" xfId="302"/>
+    <cellStyle name="常规 2 3 3 2 3" xfId="303"/>
+    <cellStyle name="常规 2 3 3 3" xfId="304"/>
+    <cellStyle name="常规 2 3 3 3 2" xfId="305"/>
+    <cellStyle name="常规 2 3 3 4" xfId="306"/>
+    <cellStyle name="常规 2 3 3 4 2" xfId="307"/>
+    <cellStyle name="常规 2 3 3 5" xfId="308"/>
+    <cellStyle name="常规 2 3 3 6" xfId="309"/>
+    <cellStyle name="常规 2 3 4" xfId="310"/>
+    <cellStyle name="常规 2 3 4 2" xfId="311"/>
+    <cellStyle name="常规 2 3 4 3" xfId="312"/>
+    <cellStyle name="常规 2 3 5" xfId="313"/>
+    <cellStyle name="常规 2 3 5 2" xfId="314"/>
+    <cellStyle name="常规 2 3 6" xfId="315"/>
+    <cellStyle name="常规 2 3 6 2" xfId="316"/>
+    <cellStyle name="常规 2 3 7" xfId="317"/>
+    <cellStyle name="常规 2 3 8" xfId="318"/>
+    <cellStyle name="常规 3" xfId="319"/>
+    <cellStyle name="常规 4" xfId="320"/>
+    <cellStyle name="常规 5" xfId="321"/>
+    <cellStyle name="常规 5 2" xfId="322"/>
+    <cellStyle name="常规 5 2 2" xfId="323"/>
+    <cellStyle name="常规 5 2 2 2" xfId="324"/>
+    <cellStyle name="常规 5 2 2 3" xfId="325"/>
+    <cellStyle name="常规 5 2 3" xfId="326"/>
+    <cellStyle name="常规 5 2 3 2" xfId="327"/>
+    <cellStyle name="常规 5 2 4" xfId="328"/>
+    <cellStyle name="常规 5 2 4 2" xfId="329"/>
+    <cellStyle name="常规 5 2 5" xfId="330"/>
+    <cellStyle name="常规 5 2 6" xfId="331"/>
+    <cellStyle name="常规 5 3" xfId="332"/>
+    <cellStyle name="常规 5 3 2" xfId="333"/>
+    <cellStyle name="常规 5 3 3" xfId="334"/>
+    <cellStyle name="常规 5 4" xfId="335"/>
+    <cellStyle name="常规 5 4 2" xfId="336"/>
+    <cellStyle name="常规 5 5" xfId="337"/>
+    <cellStyle name="常规 5 5 2" xfId="338"/>
+    <cellStyle name="常规 5 6" xfId="339"/>
+    <cellStyle name="常规 5 7" xfId="340"/>
+    <cellStyle name="常规 6" xfId="341"/>
+    <cellStyle name="注释 2" xfId="342"/>
+    <cellStyle name="注释 2 2" xfId="343"/>
+    <cellStyle name="注释 2 2 2" xfId="344"/>
+    <cellStyle name="注释 2 2 2 2" xfId="345"/>
+    <cellStyle name="注释 2 2 2 3" xfId="346"/>
+    <cellStyle name="注释 2 2 3" xfId="347"/>
+    <cellStyle name="注释 2 2 3 2" xfId="348"/>
+    <cellStyle name="注释 2 2 4" xfId="349"/>
+    <cellStyle name="注释 2 2 4 2" xfId="350"/>
+    <cellStyle name="注释 2 2 5" xfId="351"/>
+    <cellStyle name="注释 2 2 6" xfId="352"/>
+    <cellStyle name="注释 2 3" xfId="353"/>
+    <cellStyle name="注释 2 3 2" xfId="354"/>
+    <cellStyle name="注释 2 3 3" xfId="355"/>
+    <cellStyle name="注释 2 4" xfId="356"/>
+    <cellStyle name="注释 2 4 2" xfId="357"/>
+    <cellStyle name="注释 2 5" xfId="358"/>
+    <cellStyle name="注释 2 5 2" xfId="359"/>
+    <cellStyle name="注释 2 6" xfId="360"/>
+    <cellStyle name="注释 2 7" xfId="361"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <i val="0"/>
       </font>
       <fill>
@@ -1874,7 +2483,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8BF51176-8321-465F-839D-171536418616}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{445F0218-9FB7-47F7-8735-E66987B3EDDD}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1882,9 +2491,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2171,14 +2777,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B1:H111"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="18.875" customWidth="1"/>
@@ -2187,8 +2793,8 @@
     <col min="8" max="8" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1"/>
+    <row r="3" ht="20.1" customHeight="1" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2208,7 +2814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="20.1" customHeight="1" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2228,7 +2834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="20.1" customHeight="1" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -2248,7 +2854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="20.1" customHeight="1" spans="2:8">
       <c r="B6" s="6"/>
       <c r="C6" s="7">
         <v>200010</v>
@@ -2267,7 +2873,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="20.1" customHeight="1" spans="2:8">
       <c r="B7" s="6"/>
       <c r="C7" s="7">
         <v>200020</v>
@@ -2286,7 +2892,7 @@
       </c>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="20.1" customHeight="1" spans="2:8">
       <c r="B8" s="6"/>
       <c r="C8" s="7">
         <v>200030</v>
@@ -2305,13 +2911,13 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="20.1" customHeight="1" spans="2:8">
       <c r="B9" s="6"/>
       <c r="C9" s="7">
         <v>310101</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7">
         <v>310101</v>
@@ -2324,13 +2930,13 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="20.1" customHeight="1" spans="2:8">
       <c r="B10" s="6"/>
       <c r="C10" s="7">
         <v>310102</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E10" s="7">
         <v>310102</v>
@@ -2343,13 +2949,13 @@
       </c>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="20.1" customHeight="1" spans="2:8">
       <c r="B11" s="6"/>
       <c r="C11" s="7">
         <v>310103</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7">
         <v>310103</v>
@@ -2362,13 +2968,13 @@
       </c>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="20.1" customHeight="1" spans="2:8">
       <c r="B12" s="6"/>
       <c r="C12" s="7">
         <v>310104</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E12" s="7">
         <v>310104</v>
@@ -2381,13 +2987,13 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="20.1" customHeight="1" spans="2:8">
       <c r="B13" s="6"/>
       <c r="C13" s="7">
         <v>310105</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7">
         <v>310105</v>
@@ -2400,13 +3006,13 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="20.1" customHeight="1" spans="2:8">
       <c r="B14" s="6"/>
       <c r="C14" s="7">
         <v>310106</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="E14" s="7">
         <v>310106</v>
@@ -2419,13 +3025,13 @@
       </c>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="20.1" customHeight="1" spans="2:8">
       <c r="B15" s="6"/>
       <c r="C15" s="7">
         <v>310107</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E15" s="7">
         <v>310107</v>
@@ -2438,13 +3044,13 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="20.1" customHeight="1" spans="2:8">
       <c r="B16" s="6"/>
       <c r="C16" s="7">
         <v>320101</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E16" s="7">
         <v>320101</v>
@@ -2457,13 +3063,13 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="20.1" customHeight="1" spans="2:8">
       <c r="B17" s="6"/>
       <c r="C17" s="7">
         <v>320102</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E17" s="7">
         <v>320102</v>
@@ -2476,13 +3082,13 @@
       </c>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="20.1" customHeight="1" spans="2:8">
       <c r="B18" s="6"/>
       <c r="C18" s="7">
         <v>320103</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E18" s="7">
         <v>320103</v>
@@ -2495,13 +3101,13 @@
       </c>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="20.1" customHeight="1" spans="2:8">
       <c r="B19" s="6"/>
       <c r="C19" s="7">
         <v>320104</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="E19" s="7">
         <v>320104</v>
@@ -2514,13 +3120,13 @@
       </c>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="20.1" customHeight="1" spans="2:8">
       <c r="B20" s="6"/>
       <c r="C20" s="7">
         <v>320105</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="E20" s="7">
         <v>320105</v>
@@ -2533,13 +3139,13 @@
       </c>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="20.1" customHeight="1" spans="2:8">
       <c r="B21" s="6"/>
       <c r="C21" s="7">
         <v>320106</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="E21" s="7">
         <v>320106</v>
@@ -2552,13 +3158,13 @@
       </c>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="20.1" customHeight="1" spans="2:8">
       <c r="B22" s="6"/>
       <c r="C22" s="7">
         <v>320107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="E22" s="7">
         <v>320107</v>
@@ -2571,13 +3177,13 @@
       </c>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="20.1" customHeight="1" spans="2:8">
       <c r="B23" s="6"/>
       <c r="C23" s="7">
         <v>330101</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E23" s="7">
         <v>330101</v>
@@ -2590,13 +3196,13 @@
       </c>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="20.1" customHeight="1" spans="2:8">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>330102</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="E24" s="7">
         <v>330102</v>
@@ -2609,13 +3215,13 @@
       </c>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="20.1" customHeight="1" spans="2:8">
       <c r="B25" s="6"/>
       <c r="C25" s="7">
         <v>330103</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E25" s="7">
         <v>330103</v>
@@ -2628,13 +3234,13 @@
       </c>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="20.1" customHeight="1" spans="2:8">
       <c r="B26" s="6"/>
       <c r="C26" s="7">
         <v>330104</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E26" s="7">
         <v>330104</v>
@@ -2647,13 +3253,13 @@
       </c>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="20.1" customHeight="1" spans="2:8">
       <c r="B27" s="6"/>
       <c r="C27" s="7">
         <v>330105</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E27" s="7">
         <v>330105</v>
@@ -2666,13 +3272,13 @@
       </c>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="20.1" customHeight="1" spans="2:8">
       <c r="B28" s="6"/>
       <c r="C28" s="7">
         <v>330106</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E28" s="7">
         <v>330106</v>
@@ -2685,13 +3291,13 @@
       </c>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="20.1" customHeight="1" spans="2:8">
       <c r="B29" s="6"/>
       <c r="C29" s="7">
         <v>330107</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="E29" s="7">
         <v>330107</v>
@@ -2704,13 +3310,13 @@
       </c>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="20.1" customHeight="1" spans="2:8">
       <c r="B30" s="6"/>
       <c r="C30" s="7">
         <v>340101</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E30" s="7">
         <v>340101</v>
@@ -2723,13 +3329,13 @@
       </c>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="20.1" customHeight="1" spans="2:8">
       <c r="B31" s="6"/>
       <c r="C31" s="7">
         <v>340102</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="E31" s="7">
         <v>340102</v>
@@ -2742,13 +3348,13 @@
       </c>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="20.1" customHeight="1" spans="2:8">
       <c r="B32" s="6"/>
       <c r="C32" s="7">
         <v>340103</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E32" s="7">
         <v>340103</v>
@@ -2761,13 +3367,13 @@
       </c>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="20.1" customHeight="1" spans="2:8">
       <c r="B33" s="6"/>
       <c r="C33" s="7">
         <v>340104</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="E33" s="7">
         <v>340104</v>
@@ -2780,13 +3386,13 @@
       </c>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="20.1" customHeight="1" spans="2:8">
       <c r="B34" s="6"/>
       <c r="C34" s="7">
         <v>340105</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E34" s="7">
         <v>340105</v>
@@ -2799,13 +3405,13 @@
       </c>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="20.1" customHeight="1" spans="2:8">
       <c r="B35" s="6"/>
       <c r="C35" s="7">
         <v>340106</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="E35" s="7">
         <v>340106</v>
@@ -2818,13 +3424,13 @@
       </c>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="20.1" customHeight="1" spans="2:8">
       <c r="B36" s="6"/>
       <c r="C36" s="7">
         <v>340107</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E36" s="7">
         <v>340107</v>
@@ -2837,13 +3443,13 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="20.1" customHeight="1" spans="2:8">
       <c r="B37" s="6"/>
       <c r="C37" s="7">
         <v>350101</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="E37" s="7">
         <v>350101</v>
@@ -2856,13 +3462,13 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="20.1" customHeight="1" spans="2:8">
       <c r="B38" s="6"/>
       <c r="C38" s="7">
         <v>350102</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E38" s="7">
         <v>350102</v>
@@ -2875,13 +3481,13 @@
       </c>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="20.1" customHeight="1" spans="2:8">
       <c r="B39" s="6"/>
       <c r="C39" s="7">
         <v>350103</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E39" s="7">
         <v>350103</v>
@@ -2894,13 +3500,13 @@
       </c>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="20.1" customHeight="1" spans="2:8">
       <c r="B40" s="6"/>
       <c r="C40" s="7">
         <v>350104</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E40" s="7">
         <v>350104</v>
@@ -2913,13 +3519,13 @@
       </c>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="20.1" customHeight="1" spans="2:8">
       <c r="B41" s="6"/>
       <c r="C41" s="7">
         <v>350105</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E41" s="7">
         <v>350105</v>
@@ -2932,13 +3538,13 @@
       </c>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="20.1" customHeight="1" spans="2:8">
       <c r="B42" s="6"/>
       <c r="C42" s="7">
         <v>350106</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="E42" s="7">
         <v>350106</v>
@@ -2951,13 +3557,13 @@
       </c>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" ht="20.1" customHeight="1" spans="2:8">
       <c r="B43" s="6"/>
       <c r="C43" s="7">
         <v>400001</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E43" s="7">
         <v>400001</v>
@@ -2970,13 +3576,13 @@
       </c>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" ht="20.1" customHeight="1" spans="2:8">
       <c r="B44" s="6"/>
       <c r="C44" s="7">
         <v>400002</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E44" s="7">
         <v>400002</v>
@@ -2989,13 +3595,13 @@
       </c>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="20.1" customHeight="1" spans="2:8">
       <c r="B45" s="6"/>
       <c r="C45" s="7">
         <v>400003</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="E45" s="7">
         <v>400003</v>
@@ -3008,13 +3614,13 @@
       </c>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" ht="20.1" customHeight="1" spans="2:8">
       <c r="B46" s="6"/>
       <c r="C46" s="7">
         <v>400004</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="E46" s="7">
         <v>400004</v>
@@ -3027,13 +3633,13 @@
       </c>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" ht="20.1" customHeight="1" spans="2:8">
       <c r="B47" s="6"/>
       <c r="C47" s="7">
         <v>400005</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="E47" s="7">
         <v>400005</v>
@@ -3046,13 +3652,13 @@
       </c>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" ht="20.1" customHeight="1" spans="2:8">
       <c r="B48" s="6"/>
       <c r="C48" s="7">
         <v>400006</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="E48" s="7">
         <v>400006</v>
@@ -3065,13 +3671,13 @@
       </c>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" ht="20.1" customHeight="1" spans="2:8">
       <c r="B49" s="6"/>
       <c r="C49" s="7">
         <v>400007</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E49" s="7">
         <v>400007</v>
@@ -3084,13 +3690,13 @@
       </c>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" ht="20.1" customHeight="1" spans="2:8">
       <c r="B50" s="6"/>
       <c r="C50" s="7">
         <v>400008</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="E50" s="7">
         <v>400008</v>
@@ -3103,13 +3709,13 @@
       </c>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:8">
       <c r="B51" s="9"/>
       <c r="C51" s="10">
         <v>10101</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E51" s="10">
         <v>1000101</v>
@@ -3122,13 +3728,13 @@
       </c>
       <c r="H51" s="10"/>
     </row>
-    <row r="52" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:8">
       <c r="B52" s="9"/>
       <c r="C52" s="10">
         <v>10102</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="E52" s="10">
         <v>1000101</v>
@@ -3137,18 +3743,18 @@
         <v>1000101</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C53" s="10">
         <v>20101</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E53" s="10">
         <v>1000101</v>
@@ -3161,12 +3767,12 @@
       </c>
       <c r="H53" s="10"/>
     </row>
-    <row r="54" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C54" s="10">
         <v>20102</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E54" s="10">
         <v>1000101</v>
@@ -3175,18 +3781,18 @@
         <v>1000101</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C55" s="10">
         <v>30101</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E55" s="10">
         <v>1000101</v>
@@ -3199,12 +3805,12 @@
       </c>
       <c r="H55" s="10"/>
     </row>
-    <row r="56" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C56" s="10">
         <v>30102</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E56" s="10">
         <v>1000101</v>
@@ -3213,18 +3819,18 @@
         <v>1000101</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C57" s="10">
         <v>40101</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E57" s="10">
         <v>1000101</v>
@@ -3237,12 +3843,12 @@
       </c>
       <c r="H57" s="10"/>
     </row>
-    <row r="58" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C58" s="10">
         <v>40102</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E58" s="10">
         <v>1000101</v>
@@ -3251,18 +3857,18 @@
         <v>1000101</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C59" s="10">
         <v>401031</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E59" s="10">
         <v>1000101</v>
@@ -3271,18 +3877,18 @@
         <v>1000101</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C60" s="10">
         <v>401042</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E60" s="10">
         <v>1000101</v>
@@ -3291,18 +3897,18 @@
         <v>1000101</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C61" s="10">
         <v>50101</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E61" s="10">
         <v>1000101</v>
@@ -3315,12 +3921,12 @@
       </c>
       <c r="H61" s="10"/>
     </row>
-    <row r="62" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C62" s="10">
         <v>50102</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E62" s="10">
         <v>1000101</v>
@@ -3329,18 +3935,18 @@
         <v>1000101</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C63" s="10">
         <v>501031</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E63" s="10">
         <v>1000101</v>
@@ -3349,18 +3955,18 @@
         <v>1000101</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C64" s="10">
         <v>501041</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E64" s="10">
         <v>1000101</v>
@@ -3369,18 +3975,18 @@
         <v>1000101</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C65" s="10">
         <v>60101</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="E65" s="10">
         <v>1000101</v>
@@ -3393,12 +3999,12 @@
       </c>
       <c r="H65" s="10"/>
     </row>
-    <row r="66" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C66" s="10">
         <v>60102</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E66" s="10">
         <v>1000101</v>
@@ -3407,18 +4013,18 @@
         <v>1000101</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C67" s="10">
         <v>601031</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E67" s="10">
         <v>1000101</v>
@@ -3427,18 +4033,18 @@
         <v>1000101</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C68" s="10">
         <v>70101</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E68" s="10">
         <v>1000101</v>
@@ -3451,12 +4057,12 @@
       </c>
       <c r="H68" s="10"/>
     </row>
-    <row r="69" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C69" s="10">
         <v>70102</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="E69" s="10">
         <v>1000101</v>
@@ -3465,18 +4071,18 @@
         <v>1000101</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C70" s="10">
         <v>701031</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="E70" s="10">
         <v>1000101</v>
@@ -3485,18 +4091,18 @@
         <v>1000101</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C71" s="10">
         <v>701041</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="E71" s="10">
         <v>1000101</v>
@@ -3505,18 +4111,18 @@
         <v>1000101</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C72" s="10">
         <v>80101</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E72" s="10">
         <v>1000101</v>
@@ -3529,12 +4135,12 @@
       </c>
       <c r="H72" s="10"/>
     </row>
-    <row r="73" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C73" s="10">
         <v>80102</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E73" s="10">
         <v>1000101</v>
@@ -3543,18 +4149,18 @@
         <v>1000101</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C74" s="10">
         <v>90101</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E74" s="10">
         <v>1000101</v>
@@ -3567,12 +4173,12 @@
       </c>
       <c r="H74" s="10"/>
     </row>
-    <row r="75" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C75" s="10">
         <v>90102</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E75" s="10">
         <v>1000101</v>
@@ -3581,18 +4187,18 @@
         <v>1000101</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C76" s="10">
         <v>901031</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E76" s="10">
         <v>1000101</v>
@@ -3601,18 +4207,18 @@
         <v>1000101</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C77" s="10">
         <v>901041</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E77" s="10">
         <v>1000101</v>
@@ -3621,18 +4227,18 @@
         <v>1000101</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C78" s="10">
         <v>100101</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="E78" s="10">
         <v>1000101</v>
@@ -3645,12 +4251,12 @@
       </c>
       <c r="H78" s="10"/>
     </row>
-    <row r="79" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C79" s="10">
         <v>100102</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="E79" s="10">
         <v>1000101</v>
@@ -3659,18 +4265,18 @@
         <v>1000101</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="80" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C80" s="10">
         <v>1001031</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="E80" s="10">
         <v>1000101</v>
@@ -3679,18 +4285,18 @@
         <v>1000101</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C81" s="10">
         <v>1001041</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="E81" s="10">
         <v>1000101</v>
@@ -3699,18 +4305,18 @@
         <v>1000101</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C82" s="10">
         <v>110101</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="E82" s="10">
         <v>1000101</v>
@@ -3723,12 +4329,12 @@
       </c>
       <c r="H82" s="10"/>
     </row>
-    <row r="83" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C83" s="10">
         <v>110102</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="E83" s="10">
         <v>1000101</v>
@@ -3737,18 +4343,18 @@
         <v>1000101</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="84" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C84" s="10">
         <v>1101031</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="E84" s="10">
         <v>1000101</v>
@@ -3757,18 +4363,18 @@
         <v>1000101</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="85" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C85" s="10">
         <v>120101</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E85" s="10">
         <v>1000101</v>
@@ -3781,12 +4387,12 @@
       </c>
       <c r="H85" s="10"/>
     </row>
-    <row r="86" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C86" s="10">
         <v>120102</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="E86" s="10">
         <v>1000101</v>
@@ -3795,18 +4401,18 @@
         <v>1000101</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C87" s="10">
         <v>1201031</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="E87" s="10">
         <v>1000101</v>
@@ -3815,18 +4421,18 @@
         <v>1000101</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="88" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C88" s="10">
         <v>130101</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="E88" s="10">
         <v>1000101</v>
@@ -3839,12 +4445,12 @@
       </c>
       <c r="H88" s="10"/>
     </row>
-    <row r="89" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C89" s="10">
         <v>130102</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E89" s="10">
         <v>1000101</v>
@@ -3853,18 +4459,18 @@
         <v>1000101</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="90" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C90" s="10">
         <v>1301031</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E90" s="10">
         <v>1000101</v>
@@ -3873,18 +4479,18 @@
         <v>1000101</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C91" s="10">
         <v>1301041</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E91" s="10">
         <v>1000101</v>
@@ -3893,18 +4499,18 @@
         <v>1000101</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="92" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C92" s="10">
         <v>140101</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="E92" s="10">
         <v>1000101</v>
@@ -3917,12 +4523,12 @@
       </c>
       <c r="H92" s="10"/>
     </row>
-    <row r="93" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C93" s="10">
         <v>140102</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="E93" s="10">
         <v>1000101</v>
@@ -3931,18 +4537,18 @@
         <v>1000101</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C94" s="10">
         <v>1401031</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="E94" s="10">
         <v>1000101</v>
@@ -3951,18 +4557,18 @@
         <v>1000101</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C95" s="10">
         <v>910101</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E95" s="10">
         <v>1000101</v>
@@ -3975,12 +4581,12 @@
       </c>
       <c r="H95" s="10"/>
     </row>
-    <row r="96" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C96" s="10">
         <v>910102</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="E96" s="10">
         <v>1000101</v>
@@ -3989,18 +4595,18 @@
         <v>1000101</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C97" s="10">
         <v>9101031</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="E97" s="10">
         <v>1000101</v>
@@ -4009,18 +4615,18 @@
         <v>1000101</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C98" s="10">
         <v>9101041</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="E98" s="10">
         <v>1000101</v>
@@ -4029,18 +4635,18 @@
         <v>1000101</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="99" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C99" s="10">
         <v>920101</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="E99" s="10">
         <v>1000101</v>
@@ -4053,12 +4659,12 @@
       </c>
       <c r="H99" s="10"/>
     </row>
-    <row r="100" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C100" s="10">
         <v>920102</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E100" s="10">
         <v>1000101</v>
@@ -4067,18 +4673,18 @@
         <v>1000101</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="101" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C101" s="10">
         <v>9201031</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E101" s="10">
         <v>1000101</v>
@@ -4087,18 +4693,18 @@
         <v>1000101</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="102" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C102" s="10">
         <v>9201041</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E102" s="10">
         <v>1000101</v>
@@ -4107,18 +4713,18 @@
         <v>1000101</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C103" s="10">
         <v>930101</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="E103" s="10">
         <v>1000101</v>
@@ -4131,12 +4737,12 @@
       </c>
       <c r="H103" s="10"/>
     </row>
-    <row r="104" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C104" s="10">
         <v>930102</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="E104" s="10">
         <v>1000101</v>
@@ -4145,18 +4751,18 @@
         <v>1000101</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C105" s="10">
         <v>9301031</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="E105" s="10">
         <v>1000101</v>
@@ -4165,18 +4771,18 @@
         <v>1000101</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="106" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="106" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C106" s="10">
         <v>9301041</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="E106" s="10">
         <v>1000101</v>
@@ -4185,18 +4791,18 @@
         <v>1000101</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="107" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C107" s="10">
         <v>200001</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E107" s="10">
         <v>1000101</v>
@@ -4205,18 +4811,18 @@
         <v>1000101</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="108" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C108" s="10">
         <v>200002</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E108" s="10">
         <v>1000101</v>
@@ -4225,18 +4831,18 @@
         <v>1000101</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="109" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C109" s="10">
         <v>200003</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="E109" s="10">
         <v>1000101</v>
@@ -4245,17 +4851,17 @@
         <v>1000101</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="110" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110" ht="20.1" customHeight="1"/>
+    <row r="111" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>